--- a/artfynd/A 528-2024 artfynd.xlsx
+++ b/artfynd/A 528-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 528-2024 artfynd.xlsx
+++ b/artfynd/A 528-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1663873</v>
+        <v>103308398</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vingesbacke, Gstr</t>
+          <t>Vingesbackevägen, Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577067.9813379475</v>
+        <v>577031</v>
       </c>
       <c r="R2" t="n">
-        <v>6711110.222290116</v>
+        <v>6711188</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-09-11</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-09-11</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,63 +767,53 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1326188</v>
+        <v>548030</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2058</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577082.8641216684</v>
+        <v>576998</v>
       </c>
       <c r="R3" t="n">
-        <v>6711129.250672322</v>
+        <v>6711020</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-07-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-07-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +876,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>gammal granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,42 +894,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>548030</v>
+        <v>111755971</v>
       </c>
       <c r="B4" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2058</v>
+        <v>3286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,19 +932,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vingesbacke, Gstr</t>
+          <t>Storberget, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576997.8969373945</v>
+        <v>577035</v>
       </c>
       <c r="R4" t="n">
-        <v>6711020.096235071</v>
+        <v>6711054</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,77 +984,69 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>gammal granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103308398</v>
+        <v>7042069</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vingesbackevägen, Hofors, Gstr</t>
+          <t>Vingesbacke, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577030.8183931453</v>
+        <v>577090</v>
       </c>
       <c r="R5" t="n">
-        <v>6711187.718336375</v>
+        <v>6711094</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,22 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,71 +1084,76 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111755978</v>
+        <v>1326188</v>
       </c>
       <c r="B6" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storberget, Gstr</t>
+          <t>Vingesbacke, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577002</v>
+        <v>577083</v>
       </c>
       <c r="R6" t="n">
-        <v>6711039</v>
+        <v>6711129</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,12 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2012-07-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2012-07-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,53 +1193,53 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111755969</v>
+        <v>111755944</v>
       </c>
       <c r="B7" t="n">
-        <v>88966</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576993</v>
+        <v>577099</v>
       </c>
       <c r="R7" t="n">
-        <v>6711023</v>
+        <v>6711185</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1369,12 +1314,7 @@
         <v>111755945</v>
       </c>
       <c r="B8" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1336,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1409,7 +1349,7 @@
         <v>577114</v>
       </c>
       <c r="R8" t="n">
-        <v>6711160</v>
+        <v>6711161</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1468,61 +1408,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111755965</v>
+        <v>111755946</v>
       </c>
       <c r="B9" t="n">
-        <v>88966</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storberget, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577102</v>
+        <v>577063</v>
       </c>
       <c r="R9" t="n">
-        <v>6711179</v>
+        <v>6711100</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1563,7 +1487,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1582,15 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111755971</v>
+        <v>111755965</v>
       </c>
       <c r="B10" t="n">
-        <v>88899</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,26 +1516,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3286</v>
+        <v>5754</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1633,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577035</v>
+        <v>577102</v>
       </c>
       <c r="R10" t="n">
-        <v>6711053</v>
+        <v>6711179</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1696,50 +1614,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111755962</v>
+        <v>111755966</v>
       </c>
       <c r="B11" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2058</v>
+        <v>5754</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storberget, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576996</v>
+        <v>577117</v>
       </c>
       <c r="R11" t="n">
-        <v>6711029</v>
+        <v>6711191</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1775,7 +1699,7 @@
         </is>
       </c>
       <c r="AD11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
@@ -1799,37 +1723,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111755946</v>
+        <v>111755969</v>
       </c>
       <c r="B12" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>5754</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577063</v>
+        <v>576993</v>
       </c>
       <c r="R12" t="n">
-        <v>6711100</v>
+        <v>6711023</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1904,16 +1823,11 @@
         <v>111755953</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1926,12 +1840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,6 +1915,222 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>86872444</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vingesbackevägen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577009</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6711212</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I vägkanten i konkurrens med hög gräs och örtvegetation.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Barbro Risberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Barbro Risberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>111755978</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storberget, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577002</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6711039</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 528-2024 artfynd.xlsx
+++ b/artfynd/A 528-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103308398</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/548030</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755971</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7042069</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1326188</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755944</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755945</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755946</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755965</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755966</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,6 +1872,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755969</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1915,6 +1975,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755953</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2034,6 +2099,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86872444</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2131,8 +2201,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755978</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>